--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/6259-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/6259-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A08A9110-9E36-4D39-8554-C32403E98179}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1E665281-C8B4-45A2-A8F1-B79439E4E200}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{85844BB4-4FB5-44C5-9AFA-2EBC2A0DE46C}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{E47616A2-0D59-4C23-A47B-EA76BB5AAD81}"/>
   </bookViews>
   <sheets>
     <sheet name="6259-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1481,23 +1481,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E13F2A4F-E508-4D8B-9618-2EE327B514E2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDCC63B0-94E8-4EFC-8C06-6C872876BAE1}">
   <dimension ref="A1:R46"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.5546875" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="4" max="4" width="10.5" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="18" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -1525,7 +1524,7 @@
       <c r="Q1" s="31"/>
       <c r="R1" s="23"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
@@ -1555,7 +1554,7 @@
       <c r="Q2" s="33"/>
       <c r="R2" s="34"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="24" t="s">
         <v>2</v>
       </c>
@@ -1601,7 +1600,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="26"/>
       <c r="B4" s="27"/>
       <c r="C4" s="7"/>
@@ -1651,7 +1650,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="38">
         <v>2026</v>
       </c>
@@ -1705,7 +1704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>26</v>
       </c>
@@ -1761,7 +1760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="40">
         <v>2025</v>
       </c>
@@ -1815,7 +1814,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
         <v>26</v>
       </c>
@@ -1871,7 +1870,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>26</v>
       </c>
@@ -1927,7 +1926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="38">
         <v>2024</v>
       </c>
@@ -1981,7 +1980,7 @@
         <v>5.23</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>26</v>
       </c>
@@ -2037,7 +2036,7 @@
         <v>5.23</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>26</v>
       </c>
@@ -2093,7 +2092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="40">
         <v>2023</v>
       </c>
@@ -2147,7 +2146,7 @@
         <v>5.21</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
         <v>26</v>
       </c>
@@ -2203,7 +2202,7 @@
         <v>5.21</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="38">
         <v>2022</v>
       </c>
@@ -2257,7 +2256,7 @@
         <v>0.56000000000000005</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>26</v>
       </c>
@@ -2313,7 +2312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>26</v>
       </c>
@@ -2369,7 +2368,7 @@
         <v>0.56000000000000005</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="40">
         <v>2021</v>
       </c>
@@ -2423,7 +2422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="17" t="s">
         <v>26</v>
       </c>
@@ -2479,7 +2478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="s">
         <v>26</v>
       </c>
@@ -2535,7 +2534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
         <v>26</v>
       </c>
@@ -2591,7 +2590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="38">
         <v>2020</v>
       </c>
@@ -2645,7 +2644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>26</v>
       </c>
@@ -2701,7 +2700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>26</v>
       </c>
@@ -2757,7 +2756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>26</v>
       </c>
@@ -2813,7 +2812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="40">
         <v>2019</v>
       </c>
@@ -2867,7 +2866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="38">
         <v>2018</v>
       </c>
@@ -2921,7 +2920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="40">
         <v>2017</v>
       </c>
@@ -2975,7 +2974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="38">
         <v>2016</v>
       </c>
@@ -3029,7 +3028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="40">
         <v>2015</v>
       </c>
@@ -3083,7 +3082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="38">
         <v>2014</v>
       </c>
@@ -3137,7 +3136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="40">
         <v>2013</v>
       </c>
@@ -3191,7 +3190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="38">
         <v>2012</v>
       </c>
@@ -3245,7 +3244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="40">
         <v>2011</v>
       </c>
@@ -3299,7 +3298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="38">
         <v>2010</v>
       </c>
@@ -3353,7 +3352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="40">
         <v>2009</v>
       </c>
@@ -3407,7 +3406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="38">
         <v>2008</v>
       </c>
@@ -3461,7 +3460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="40">
         <v>2007</v>
       </c>
@@ -3515,7 +3514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="38">
         <v>2006</v>
       </c>
@@ -3569,7 +3568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="40">
         <v>2005</v>
       </c>
@@ -3623,7 +3622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="38">
         <v>2004</v>
       </c>
@@ -3677,7 +3676,7 @@
         <v>7.07</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="40">
         <v>2003</v>
       </c>
@@ -3731,7 +3730,7 @@
         <v>2.65</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="38">
         <v>2002</v>
       </c>
@@ -3785,7 +3784,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="40">
         <v>2001</v>
       </c>
@@ -3839,7 +3838,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="38">
         <v>2000</v>
       </c>
@@ -3893,7 +3892,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="40" t="s">
         <v>45</v>
       </c>
